--- a/Backtest/05-03-21/S&P500stock_05-03-21period252RS90.xlsx
+++ b/Backtest/05-03-21/S&P500stock_05-03-21period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="91">
   <si>
     <t>Stock</t>
   </si>
@@ -130,67 +130,115 @@
     <t>FCX</t>
   </si>
   <si>
-    <t>ON</t>
-  </si>
-  <si>
-    <t>GNRC</t>
+    <t>FDX</t>
+  </si>
+  <si>
+    <t>COF</t>
+  </si>
+  <si>
+    <t>DFS</t>
+  </si>
+  <si>
+    <t>KKR</t>
+  </si>
+  <si>
+    <t>IVZ</t>
+  </si>
+  <si>
+    <t>STLD</t>
+  </si>
+  <si>
+    <t>FITB</t>
+  </si>
+  <si>
+    <t>CRL</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t>NWSA</t>
   </si>
   <si>
     <t>PWR</t>
   </si>
   <si>
-    <t>NWSA</t>
+    <t>CARR</t>
   </si>
   <si>
     <t>AMAT</t>
   </si>
   <si>
-    <t>MS</t>
+    <t>BG</t>
   </si>
   <si>
     <t>MOS</t>
   </si>
   <si>
-    <t>EQT</t>
-  </si>
-  <si>
-    <t>inf</t>
-  </si>
-  <si>
-    <t>2021-04-22</t>
-  </si>
-  <si>
-    <t>2021-05-03</t>
-  </si>
-  <si>
-    <t>2021-04-29</t>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>BLDR</t>
+  </si>
+  <si>
+    <t>TRGP</t>
+  </si>
+  <si>
+    <t>2021-07-22</t>
+  </si>
+  <si>
+    <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
+    <t>2021-05-04</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
+    <t>2021-07-19</t>
+  </si>
+  <si>
+    <t>2021-07-28</t>
   </si>
   <si>
     <t>2021-05-06</t>
   </si>
   <si>
+    <t>2021-07-29</t>
+  </si>
+  <si>
     <t>2021-05-20</t>
   </si>
   <si>
-    <t>2021-04-16</t>
-  </si>
-  <si>
-    <t>2021-05-05</t>
+    <t>2021-08-02</t>
   </si>
   <si>
     <t>Basic Materials</t>
   </si>
   <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
     <t>Technology</t>
   </si>
   <si>
-    <t>Industrials</t>
-  </si>
-  <si>
     <t>Communication Services</t>
   </si>
   <si>
-    <t>Financial Services</t>
+    <t>Consumer Defensive</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
   </si>
   <si>
     <t>Energy</t>
@@ -199,28 +247,46 @@
     <t>Copper</t>
   </si>
   <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>Specialty Industrial Machinery</t>
+    <t>Integrated Freight &amp; Logistics</t>
+  </si>
+  <si>
+    <t>Credit Services</t>
+  </si>
+  <si>
+    <t>Asset Management</t>
+  </si>
+  <si>
+    <t>Steel</t>
+  </si>
+  <si>
+    <t>Banks - Regional</t>
+  </si>
+  <si>
+    <t>Diagnostics &amp; Research</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment &amp; Materials</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
   </si>
   <si>
     <t>Engineering &amp; Construction</t>
   </si>
   <si>
-    <t>Entertainment</t>
-  </si>
-  <si>
-    <t>Semiconductor Equipment &amp; Materials</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
+    <t>Building Products &amp; Equipment</t>
+  </si>
+  <si>
+    <t>Farm Products</t>
   </si>
   <si>
     <t>Agricultural Inputs</t>
   </si>
   <si>
-    <t>Oil &amp; Gas E&amp;P</t>
+    <t>Footwear &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Midstream</t>
   </si>
 </sst>
 </file>
@@ -578,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK10"/>
+  <dimension ref="A1:AK20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -699,43 +765,43 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>99.39516129032258</v>
+        <v>99.5959595959596</v>
       </c>
       <c r="C2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2">
-        <v>32.7</v>
+        <v>37.71</v>
       </c>
       <c r="E2">
-        <v>3.97</v>
+        <v>3.42</v>
       </c>
       <c r="F2">
-        <v>0.5259142870882891</v>
+        <v>3.299227959196955</v>
       </c>
       <c r="G2">
-        <v>3.63</v>
+        <v>3.74</v>
       </c>
       <c r="H2">
-        <v>0.8882107032427138</v>
+        <v>2.042599181727492</v>
       </c>
       <c r="I2">
-        <v>34.33800048828125</v>
+        <v>38.63999938964844</v>
       </c>
       <c r="J2">
-        <v>33.95000019073486</v>
+        <v>36.3015001296997</v>
       </c>
       <c r="K2">
-        <v>30.54280010223389</v>
+        <v>35.40400009155273</v>
       </c>
       <c r="L2">
-        <v>19.43665001392365</v>
+        <v>24.32215002059937</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N2">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -756,52 +822,52 @@
         <v>0</v>
       </c>
       <c r="V2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="b">
         <v>1</v>
       </c>
       <c r="X2">
-        <v>4.82</v>
+        <v>7.81</v>
       </c>
       <c r="Y2">
-        <v>39.1</v>
+        <v>39.98</v>
       </c>
       <c r="Z2">
-        <v>38.02</v>
+        <v>48.64</v>
       </c>
       <c r="AA2">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="AB2">
-        <v>180.39</v>
+        <v>348</v>
       </c>
       <c r="AC2">
-        <v>247.06</v>
+        <v>1533.33</v>
       </c>
       <c r="AD2">
-        <v>4.6</v>
+        <v>4.87</v>
       </c>
       <c r="AE2">
+        <v>-2</v>
+      </c>
+      <c r="AF2">
         <v>127.27</v>
       </c>
-      <c r="AF2">
+      <c r="AG2">
         <v>633.33</v>
       </c>
-      <c r="AG2">
-        <v>108.82</v>
-      </c>
       <c r="AH2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="AI2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="AJ2" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="AK2">
-        <v>75.10307398741071</v>
+        <v>82.80311840495418</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -809,43 +875,43 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>95.96774193548387</v>
+        <v>92.52525252525253</v>
       </c>
       <c r="C3">
-        <v>98</v>
+        <v>208</v>
       </c>
       <c r="D3">
-        <v>37.04</v>
+        <v>290.31</v>
       </c>
       <c r="E3">
-        <v>3.82</v>
+        <v>1.59</v>
       </c>
       <c r="F3">
-        <v>0.4028667502478746</v>
+        <v>-0.3482809801123652</v>
       </c>
       <c r="G3">
-        <v>2.83</v>
+        <v>1.91</v>
       </c>
       <c r="H3">
-        <v>-0.1601691432077026</v>
+        <v>-0.5917173445582978</v>
       </c>
       <c r="I3">
-        <v>39.93800048828125</v>
+        <v>287.406005859375</v>
       </c>
       <c r="J3">
-        <v>40.10250015258789</v>
+        <v>284.7655029296875</v>
       </c>
       <c r="K3">
-        <v>37.03840007781982</v>
+        <v>273.1684017944336</v>
       </c>
       <c r="L3">
-        <v>26.47145004749298</v>
+        <v>253.2176502990723</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -866,52 +932,52 @@
         <v>0</v>
       </c>
       <c r="V3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>8.17</v>
+        <v>103.4</v>
       </c>
       <c r="Y3">
-        <v>42.38</v>
+        <v>305.66</v>
       </c>
       <c r="Z3">
-        <v>13.71</v>
+        <v>68.72</v>
       </c>
       <c r="AA3">
-        <v>33.89</v>
+        <v>19.24</v>
       </c>
       <c r="AB3">
-        <v>16.33</v>
+        <v>547.27</v>
       </c>
       <c r="AC3">
-        <v>800</v>
+        <v>358.46</v>
       </c>
       <c r="AD3">
-        <v>2.52</v>
+        <v>4.06</v>
       </c>
       <c r="AE3">
-        <v>-46.15</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>46</v>
+        <v>-27.59</v>
+      </c>
+      <c r="AF3">
+        <v>-2.32</v>
       </c>
       <c r="AG3">
-        <v>100</v>
+        <v>465.38</v>
       </c>
       <c r="AH3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="AI3" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="AJ3" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="AK3">
-        <v>54.11702604748056</v>
+        <v>74.25291644325843</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -919,43 +985,43 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>98.18548387096774</v>
+        <v>92.92929292929293</v>
       </c>
       <c r="C4">
-        <v>435</v>
+        <v>162</v>
       </c>
       <c r="D4">
-        <v>305.72</v>
+        <v>149.08</v>
       </c>
       <c r="E4">
-        <v>4.88</v>
+        <v>1.63</v>
       </c>
       <c r="F4">
-        <v>1.272402677253468</v>
+        <v>-0.2685540087613422</v>
       </c>
       <c r="G4">
-        <v>3.69</v>
+        <v>1.83</v>
       </c>
       <c r="H4">
-        <v>0.9668391917264951</v>
+        <v>-0.7068787227565835</v>
       </c>
       <c r="I4">
-        <v>327.6980041503906</v>
+        <v>143.9819976806641</v>
       </c>
       <c r="J4">
-        <v>318.7610000610351</v>
+        <v>136.356999206543</v>
       </c>
       <c r="K4">
-        <v>276.9283975219727</v>
+        <v>130.3976002502442</v>
       </c>
       <c r="L4">
-        <v>198.6924991989136</v>
+        <v>95.76575000762939</v>
       </c>
       <c r="M4">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -976,52 +1042,52 @@
         <v>0</v>
       </c>
       <c r="V4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>75.5</v>
+        <v>51.91</v>
       </c>
       <c r="Y4">
-        <v>364</v>
+        <v>150.01</v>
       </c>
       <c r="Z4">
-        <v>14.49</v>
+        <v>58.54</v>
       </c>
       <c r="AA4">
-        <v>67.42</v>
+        <v>4.08</v>
       </c>
       <c r="AB4">
-        <v>17.36</v>
+        <v>425.68</v>
       </c>
       <c r="AC4">
-        <v>192.75</v>
+        <v>419.46</v>
       </c>
       <c r="AD4">
-        <v>8.99</v>
+        <v>5.44</v>
       </c>
       <c r="AE4">
-        <v>8.6</v>
+        <v>30.02</v>
       </c>
       <c r="AF4">
-        <v>78.84999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="AG4">
-        <v>50.72</v>
+        <v>329.41</v>
       </c>
       <c r="AH4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="AI4" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="AJ4" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="AK4">
-        <v>36.96202591948553</v>
+        <v>72.8158951553991</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1029,49 +1095,49 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>96.37096774193549</v>
+        <v>96.76767676767678</v>
       </c>
       <c r="C5">
-        <v>329</v>
+        <v>217</v>
       </c>
       <c r="D5">
-        <v>81.83</v>
+        <v>114</v>
       </c>
       <c r="E5">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="F5">
-        <v>-1.328001934640618</v>
+        <v>-0.02937309470827178</v>
       </c>
       <c r="G5">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="H5">
-        <v>-0.9333492799648846</v>
+        <v>-0.3757897604365116</v>
       </c>
       <c r="I5">
-        <v>83.66399993896485</v>
+        <v>110.768000793457</v>
       </c>
       <c r="J5">
-        <v>79.19300003051758</v>
+        <v>102.7069999694824</v>
       </c>
       <c r="K5">
-        <v>75.87880004882813</v>
+        <v>99.05759994506836</v>
       </c>
       <c r="L5">
-        <v>57.87010007858277</v>
+        <v>77.72375007629394</v>
       </c>
       <c r="M5">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1080,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
@@ -1089,49 +1155,49 @@
         <v>1</v>
       </c>
       <c r="W5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5">
-        <v>23.77</v>
+        <v>35.05</v>
       </c>
       <c r="Y5">
-        <v>87.67</v>
+        <v>114.8</v>
       </c>
       <c r="Z5">
-        <v>10.46</v>
+        <v>29.16</v>
       </c>
       <c r="AA5">
-        <v>21.3</v>
+        <v>3.98</v>
       </c>
       <c r="AB5">
-        <v>3.96</v>
+        <v>61.93</v>
       </c>
       <c r="AC5">
-        <v>340.74</v>
+        <v>520</v>
       </c>
       <c r="AD5">
-        <v>3.95</v>
+        <v>14.35</v>
       </c>
       <c r="AE5">
-        <v>2.59</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="AF5">
-        <v>118.87</v>
+        <v>6.12</v>
       </c>
       <c r="AG5">
-        <v>96.3</v>
+        <v>304.17</v>
       </c>
       <c r="AH5" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="AI5" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="AJ5" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="AK5">
-        <v>24.17465745576716</v>
+        <v>55.81992831467431</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1139,43 +1205,43 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>96.16935483870968</v>
+        <v>91.71717171717172</v>
       </c>
       <c r="C6">
-        <v>176</v>
+        <v>252</v>
       </c>
       <c r="D6">
-        <v>23.53</v>
+        <v>56.58</v>
       </c>
       <c r="E6">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="F6">
-        <v>-0.8604212946470446</v>
+        <v>-1.504322064702205</v>
       </c>
       <c r="G6">
-        <v>1.88</v>
+        <v>1.38</v>
       </c>
       <c r="H6">
-        <v>-1.405120210867572</v>
+        <v>-1.354661475121942</v>
       </c>
       <c r="I6">
-        <v>23.75400047302246</v>
+        <v>56.4620002746582</v>
       </c>
       <c r="J6">
-        <v>22.97400016784668</v>
+        <v>53.49249992370606</v>
       </c>
       <c r="K6">
-        <v>20.38560009002686</v>
+        <v>49.9231997680664</v>
       </c>
       <c r="L6">
-        <v>15.81425002574921</v>
+        <v>40.87424997329712</v>
       </c>
       <c r="M6">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N6">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -1187,10 +1253,10 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>6.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -1202,46 +1268,46 @@
         <v>1</v>
       </c>
       <c r="X6">
-        <v>7.9</v>
+        <v>23.43</v>
       </c>
       <c r="Y6">
-        <v>24.5</v>
+        <v>57.18</v>
       </c>
       <c r="Z6">
-        <v>10.65</v>
+        <v>23.63</v>
       </c>
       <c r="AA6">
-        <v>138.94</v>
+        <v>532.41</v>
       </c>
       <c r="AB6">
-        <v>4.55</v>
+        <v>163.36</v>
       </c>
       <c r="AC6">
-        <v>131.45</v>
+        <v>214.72</v>
       </c>
       <c r="AD6">
-        <v>2.88</v>
+        <v>11.28</v>
       </c>
       <c r="AE6">
-        <v>550</v>
+        <v>42.47</v>
       </c>
       <c r="AF6">
-        <v>108.82</v>
+        <v>48.8</v>
       </c>
       <c r="AG6">
-        <v>45.16</v>
+        <v>154.11</v>
       </c>
       <c r="AH6" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="AI6" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="AJ6" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="AK6">
-        <v>23.84631520137689</v>
+        <v>55.30524103583217</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1249,46 +1315,46 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>93.54838709677419</v>
+        <v>98.7878787878788</v>
       </c>
       <c r="C7">
-        <v>82</v>
+        <v>145</v>
       </c>
       <c r="D7">
-        <v>108.24</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>4.1</v>
+        <v>1.87</v>
       </c>
       <c r="F7">
-        <v>0.6325554856833143</v>
+        <v>0.2098078193447986</v>
       </c>
       <c r="G7">
-        <v>3.23</v>
+        <v>2.39</v>
       </c>
       <c r="H7">
-        <v>0.3640207800175057</v>
+        <v>0.09925092463141777</v>
       </c>
       <c r="I7">
-        <v>116.3240005493164</v>
+        <v>26.96999969482422</v>
       </c>
       <c r="J7">
-        <v>113.3889995574951</v>
+        <v>26.38599996566773</v>
       </c>
       <c r="K7">
-        <v>103.201600189209</v>
+        <v>25.12159992218018</v>
       </c>
       <c r="L7">
-        <v>74.50335021972656</v>
+        <v>17.39394998550415</v>
       </c>
       <c r="M7">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N7">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1300,58 +1366,58 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>0.5555555555555555</v>
+        <v>0</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>36.64</v>
+        <v>6.38</v>
       </c>
       <c r="Y7">
-        <v>124.5</v>
+        <v>27.68</v>
       </c>
       <c r="Z7">
-        <v>89.43000000000001</v>
+        <v>11.72</v>
       </c>
       <c r="AA7">
-        <v>43.58</v>
+        <v>4.63</v>
       </c>
       <c r="AB7">
-        <v>8.789999999999999</v>
+        <v>37.5</v>
       </c>
       <c r="AC7">
-        <v>50</v>
+        <v>544.4400000000001</v>
       </c>
       <c r="AD7">
-        <v>9.85</v>
+        <v>3.37</v>
       </c>
       <c r="AE7">
-        <v>-0.8100000000000001</v>
+        <v>28.89</v>
       </c>
       <c r="AF7">
-        <v>34.78</v>
+        <v>7.14</v>
       </c>
       <c r="AG7">
-        <v>12.2</v>
+        <v>366.67</v>
       </c>
       <c r="AH7" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="AI7" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="AJ7" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="AK7">
-        <v>11.22372859754458</v>
+        <v>47.18000358017645</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1359,43 +1425,43 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>93.95161290322581</v>
+        <v>91.51515151515152</v>
       </c>
       <c r="C8">
-        <v>44</v>
+        <v>205</v>
       </c>
       <c r="D8">
-        <v>81.11</v>
+        <v>54.22</v>
       </c>
       <c r="E8">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="F8">
-        <v>-1.459252640603727</v>
+        <v>0.2696030478580658</v>
       </c>
       <c r="G8">
-        <v>1.94</v>
+        <v>2.47</v>
       </c>
       <c r="H8">
-        <v>-1.326491722383791</v>
+        <v>0.2144123028297037</v>
       </c>
       <c r="I8">
-        <v>79.99800109863281</v>
+        <v>54.8620002746582</v>
       </c>
       <c r="J8">
-        <v>76.60850067138672</v>
+        <v>52.02999992370606</v>
       </c>
       <c r="K8">
-        <v>73.44299972534179</v>
+        <v>48.67639991760254</v>
       </c>
       <c r="L8">
-        <v>57.0639500617981</v>
+        <v>37.32694993019104</v>
       </c>
       <c r="M8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -1404,13 +1470,13 @@
         <v>0</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
@@ -1419,49 +1485,49 @@
         <v>1</v>
       </c>
       <c r="W8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8">
-        <v>27.2</v>
+        <v>20.97</v>
       </c>
       <c r="Y8">
-        <v>83.48</v>
+        <v>55.93</v>
       </c>
       <c r="Z8">
-        <v>111.29</v>
+        <v>10.77</v>
       </c>
       <c r="AA8">
-        <v>10.51</v>
+        <v>2609</v>
       </c>
       <c r="AB8">
-        <v>4.3</v>
+        <v>11.21</v>
       </c>
       <c r="AC8">
-        <v>83.33</v>
+        <v>466.67</v>
       </c>
       <c r="AD8">
-        <v>3.63</v>
+        <v>9.6</v>
       </c>
       <c r="AE8">
-        <v>11.31</v>
+        <v>129.21</v>
       </c>
       <c r="AF8">
-        <v>-15.15</v>
+        <v>85.42</v>
       </c>
       <c r="AG8">
-        <v>94.12</v>
+        <v>33.33</v>
       </c>
       <c r="AH8" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="AI8" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="AJ8" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="AK8">
-        <v>7.404466179402203</v>
+        <v>37.2906030530385</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1469,109 +1535,109 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>91.53225806451613</v>
+        <v>90.90909090909091</v>
       </c>
       <c r="C9">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D9">
-        <v>29.57</v>
+        <v>40.54</v>
       </c>
       <c r="E9">
-        <v>4.48</v>
+        <v>1.71</v>
       </c>
       <c r="F9">
-        <v>0.9442759123456976</v>
+        <v>-0.1091000660592953</v>
       </c>
       <c r="G9">
-        <v>3.31</v>
+        <v>2.01</v>
       </c>
       <c r="H9">
-        <v>0.4688587646625474</v>
+        <v>-0.4477656218104407</v>
       </c>
       <c r="I9">
-        <v>30.49399948120117</v>
+        <v>39.81599960327149</v>
       </c>
       <c r="J9">
-        <v>29.47949991226196</v>
+        <v>38.46699981689453</v>
       </c>
       <c r="K9">
-        <v>27.35139987945557</v>
+        <v>37.57959999084473</v>
       </c>
       <c r="L9">
-        <v>19.5280499458313</v>
+        <v>27.97725002288819</v>
       </c>
       <c r="M9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N9">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
       <c r="V9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>6.5</v>
+        <v>14.89</v>
       </c>
       <c r="Y9">
-        <v>33.23</v>
+        <v>40.96</v>
       </c>
       <c r="Z9">
-        <v>8.77</v>
+        <v>27.09</v>
       </c>
       <c r="AA9">
-        <v>2.84</v>
+        <v>9.44</v>
       </c>
       <c r="AB9">
-        <v>153.01</v>
+        <v>9.16</v>
       </c>
       <c r="AC9">
-        <v>505.56</v>
+        <v>308.7</v>
       </c>
       <c r="AD9">
-        <v>8.49</v>
+        <v>3.39</v>
       </c>
       <c r="AE9">
-        <v>11050</v>
+        <v>18.99</v>
       </c>
       <c r="AF9">
-        <v>-115.38</v>
+        <v>1.28</v>
       </c>
       <c r="AG9">
-        <v>124.07</v>
+        <v>239.13</v>
       </c>
       <c r="AH9" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="AI9" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="AJ9" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="AK9">
-        <v>81.67622071065151</v>
+        <v>31.2144781717331</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1579,40 +1645,40 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>98.99193548387096</v>
+        <v>92.72727272727272</v>
       </c>
       <c r="C10">
-        <v>134</v>
+        <v>480</v>
       </c>
       <c r="D10">
-        <v>18.31</v>
+        <v>332.45</v>
       </c>
       <c r="E10">
-        <v>3.17</v>
+        <v>1.3</v>
       </c>
       <c r="F10">
-        <v>-0.1303392427272535</v>
+        <v>-0.926301522407285</v>
       </c>
       <c r="G10">
-        <v>3.82</v>
+        <v>1.77</v>
       </c>
       <c r="H10">
-        <v>1.137200916774688</v>
+        <v>-0.7932497564052979</v>
       </c>
       <c r="I10">
-        <v>18.28000030517578</v>
+        <v>334.3859985351563</v>
       </c>
       <c r="J10">
-        <v>17.78700008392334</v>
+        <v>319.0565017700195</v>
       </c>
       <c r="K10">
-        <v>16.33339998245239</v>
+        <v>298.0946008300782</v>
       </c>
       <c r="L10">
-        <v>14.89339997291565</v>
+        <v>251.6346501922608</v>
       </c>
       <c r="M10">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N10">
         <v>1.12</v>
@@ -1633,55 +1699,1155 @@
         <v>0</v>
       </c>
       <c r="U10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="b">
         <v>1</v>
       </c>
       <c r="W10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10">
-        <v>4.9</v>
+        <v>136</v>
       </c>
       <c r="Y10">
+        <v>337.48</v>
+      </c>
+      <c r="Z10">
+        <v>12.65</v>
+      </c>
+      <c r="AA10">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="AB10">
+        <v>18.55</v>
+      </c>
+      <c r="AC10">
+        <v>180.58</v>
+      </c>
+      <c r="AD10">
+        <v>6.81</v>
+      </c>
+      <c r="AE10">
+        <v>39.61</v>
+      </c>
+      <c r="AF10">
+        <v>52.21</v>
+      </c>
+      <c r="AG10">
+        <v>32.04</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK10">
+        <v>28.77699358104677</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11">
+        <v>94.74747474747474</v>
+      </c>
+      <c r="C11">
+        <v>50</v>
+      </c>
+      <c r="D11">
+        <v>62.04</v>
+      </c>
+      <c r="E11">
+        <v>2.27</v>
+      </c>
+      <c r="F11">
+        <v>1.007077532855033</v>
+      </c>
+      <c r="G11">
+        <v>3.6</v>
+      </c>
+      <c r="H11">
+        <v>1.841066769880492</v>
+      </c>
+      <c r="I11">
+        <v>63.75039978027344</v>
+      </c>
+      <c r="J11">
+        <v>64.1826000213623</v>
+      </c>
+      <c r="K11">
+        <v>59.17403991699219</v>
+      </c>
+      <c r="L11">
+        <v>46.1732998752594</v>
+      </c>
+      <c r="M11">
+        <v>0.99</v>
+      </c>
+      <c r="N11">
+        <v>1.08</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11" t="b">
+        <v>1</v>
+      </c>
+      <c r="V11" t="b">
+        <v>0</v>
+      </c>
+      <c r="W11" t="b">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>22.97</v>
+      </c>
+      <c r="Y11">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="Z11">
+        <v>86.08</v>
+      </c>
+      <c r="AA11">
+        <v>110.96</v>
+      </c>
+      <c r="AB11">
+        <v>25.1</v>
+      </c>
+      <c r="AC11">
+        <v>56.46</v>
+      </c>
+      <c r="AD11">
+        <v>19.93</v>
+      </c>
+      <c r="AE11">
+        <v>24.34</v>
+      </c>
+      <c r="AF11">
+        <v>6.53</v>
+      </c>
+      <c r="AG11">
+        <v>18.12</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK11">
+        <v>21.18961242034923</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12">
+        <v>96.36363636363636</v>
+      </c>
+      <c r="C12">
+        <v>178</v>
+      </c>
+      <c r="D12">
+        <v>26.2</v>
+      </c>
+      <c r="E12">
+        <v>1.26</v>
+      </c>
+      <c r="F12">
+        <v>-1.006028493758309</v>
+      </c>
+      <c r="G12">
+        <v>1.94</v>
+      </c>
+      <c r="H12">
+        <v>-0.5485318277339406</v>
+      </c>
+      <c r="I12">
+        <v>26.42000007629395</v>
+      </c>
+      <c r="J12">
+        <v>26.58449993133545</v>
+      </c>
+      <c r="K12">
+        <v>25.67</v>
+      </c>
+      <c r="L12">
+        <v>18.64915001869202</v>
+      </c>
+      <c r="M12">
+        <v>0.99</v>
+      </c>
+      <c r="N12">
+        <v>1.03</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>4</v>
+      </c>
+      <c r="T12">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="U12" t="b">
+        <v>1</v>
+      </c>
+      <c r="V12" t="b">
+        <v>0</v>
+      </c>
+      <c r="W12" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y12">
+        <v>27.68</v>
+      </c>
+      <c r="Z12">
+        <v>10.65</v>
+      </c>
+      <c r="AA12">
+        <v>138.94</v>
+      </c>
+      <c r="AB12">
+        <v>4.55</v>
+      </c>
+      <c r="AC12">
+        <v>131.45</v>
+      </c>
+      <c r="AD12">
+        <v>2.88</v>
+      </c>
+      <c r="AE12">
+        <v>550</v>
+      </c>
+      <c r="AF12">
+        <v>108.82</v>
+      </c>
+      <c r="AG12">
+        <v>45.16</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>72</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK12">
+        <v>21.05218649559833</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13">
+        <v>96.96969696969697</v>
+      </c>
+      <c r="C13">
+        <v>375</v>
+      </c>
+      <c r="D13">
+        <v>96.64</v>
+      </c>
+      <c r="E13">
+        <v>1.34</v>
+      </c>
+      <c r="F13">
+        <v>-0.8465745510562616</v>
+      </c>
+      <c r="G13">
+        <v>1.7</v>
+      </c>
+      <c r="H13">
+        <v>-0.8940159623287982</v>
+      </c>
+      <c r="I13">
+        <v>97.8259994506836</v>
+      </c>
+      <c r="J13">
+        <v>95.02799949645996</v>
+      </c>
+      <c r="K13">
+        <v>88.67819992065429</v>
+      </c>
+      <c r="L13">
+        <v>68.31480010986328</v>
+      </c>
+      <c r="M13">
+        <v>1.03</v>
+      </c>
+      <c r="N13">
+        <v>1.1</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13" t="b">
+        <v>0</v>
+      </c>
+      <c r="V13" t="b">
+        <v>1</v>
+      </c>
+      <c r="W13" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>28.71</v>
+      </c>
+      <c r="Y13">
+        <v>98.95</v>
+      </c>
+      <c r="Z13">
+        <v>10.46</v>
+      </c>
+      <c r="AA13">
+        <v>21.3</v>
+      </c>
+      <c r="AB13">
+        <v>3.96</v>
+      </c>
+      <c r="AC13">
+        <v>340.74</v>
+      </c>
+      <c r="AD13">
+        <v>3.95</v>
+      </c>
+      <c r="AE13">
+        <v>2.59</v>
+      </c>
+      <c r="AF13">
+        <v>118.87</v>
+      </c>
+      <c r="AG13">
+        <v>96.3</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>85</v>
+      </c>
+      <c r="AK13">
+        <v>18.77116302287217</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14">
+        <v>95.35353535353536</v>
+      </c>
+      <c r="C14">
+        <v>91</v>
+      </c>
+      <c r="D14">
+        <v>43.58</v>
+      </c>
+      <c r="E14">
+        <v>1.35</v>
+      </c>
+      <c r="F14">
+        <v>-0.8266428082185057</v>
+      </c>
+      <c r="G14">
+        <v>1.9</v>
+      </c>
+      <c r="H14">
+        <v>-0.6061125168330835</v>
+      </c>
+      <c r="I14">
+        <v>44.25600051879883</v>
+      </c>
+      <c r="J14">
+        <v>43.40050029754639</v>
+      </c>
+      <c r="K14">
+        <v>40.75039993286133</v>
+      </c>
+      <c r="L14">
+        <v>35.83329996109009</v>
+      </c>
+      <c r="M14">
+        <v>1.02</v>
+      </c>
+      <c r="N14">
+        <v>1.09</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14" t="b">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>15.43</v>
+      </c>
+      <c r="Y14">
+        <v>45.32</v>
+      </c>
+      <c r="Z14">
+        <v>37.57</v>
+      </c>
+      <c r="AA14">
+        <v>0.21</v>
+      </c>
+      <c r="AB14">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="AC14">
+        <v>46.67</v>
+      </c>
+      <c r="AD14">
+        <v>5.75</v>
+      </c>
+      <c r="AE14">
+        <v>-56.86</v>
+      </c>
+      <c r="AF14">
+        <v>18.6</v>
+      </c>
+      <c r="AG14">
+        <v>186.67</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK14">
+        <v>8.899066429208782</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15">
+        <v>97.17171717171718</v>
+      </c>
+      <c r="C15">
+        <v>84</v>
+      </c>
+      <c r="D15">
+        <v>132.71</v>
+      </c>
+      <c r="E15">
+        <v>1.87</v>
+      </c>
+      <c r="F15">
+        <v>0.2098078193447986</v>
+      </c>
+      <c r="G15">
+        <v>3.53</v>
+      </c>
+      <c r="H15">
+        <v>1.740300563956991</v>
+      </c>
+      <c r="I15">
+        <v>135.5740020751953</v>
+      </c>
+      <c r="J15">
+        <v>135.5690010070801</v>
+      </c>
+      <c r="K15">
+        <v>125.4652006530762</v>
+      </c>
+      <c r="L15">
+        <v>88.21640031814576</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1.08</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15" t="b">
+        <v>0</v>
+      </c>
+      <c r="V15" t="b">
+        <v>0</v>
+      </c>
+      <c r="W15" t="b">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>46.22</v>
+      </c>
+      <c r="Y15">
+        <v>146</v>
+      </c>
+      <c r="Z15">
+        <v>89.43000000000001</v>
+      </c>
+      <c r="AA15">
+        <v>43.58</v>
+      </c>
+      <c r="AB15">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="AC15">
+        <v>50</v>
+      </c>
+      <c r="AD15">
+        <v>9.85</v>
+      </c>
+      <c r="AE15">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="AF15">
+        <v>34.78</v>
+      </c>
+      <c r="AG15">
+        <v>12.2</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK15">
+        <v>8.591340369128977</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37">
+      <c r="A16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16">
+        <v>90.1010101010101</v>
+      </c>
+      <c r="C16">
+        <v>318</v>
+      </c>
+      <c r="D16">
+        <v>84.42</v>
+      </c>
+      <c r="E16">
+        <v>1.81</v>
+      </c>
+      <c r="F16">
+        <v>0.09021736231826344</v>
+      </c>
+      <c r="G16">
+        <v>1.82</v>
+      </c>
+      <c r="H16">
+        <v>-0.7212738950313692</v>
+      </c>
+      <c r="I16">
+        <v>85.98399963378907</v>
+      </c>
+      <c r="J16">
+        <v>82.09150009155273</v>
+      </c>
+      <c r="K16">
+        <v>79.76839981079101</v>
+      </c>
+      <c r="L16">
+        <v>62.24009998321533</v>
+      </c>
+      <c r="M16">
+        <v>1.05</v>
+      </c>
+      <c r="N16">
+        <v>1.08</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="U16" t="b">
+        <v>0</v>
+      </c>
+      <c r="V16" t="b">
+        <v>0</v>
+      </c>
+      <c r="W16" t="b">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>32.68</v>
+      </c>
+      <c r="Y16">
+        <v>88.84</v>
+      </c>
+      <c r="Z16">
+        <v>9.82</v>
+      </c>
+      <c r="AA16">
+        <v>3.54</v>
+      </c>
+      <c r="AB16">
+        <v>173.8</v>
+      </c>
+      <c r="AC16">
+        <v>367.81</v>
+      </c>
+      <c r="AD16">
+        <v>10.32</v>
+      </c>
+      <c r="AE16">
+        <v>105.79</v>
+      </c>
+      <c r="AF16">
+        <v>-47.51</v>
+      </c>
+      <c r="AG16">
+        <v>347.95</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>73</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>87</v>
+      </c>
+      <c r="AK16">
+        <v>62.8025388885188</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37">
+      <c r="A17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17">
+        <v>98.38383838383838</v>
+      </c>
+      <c r="C17">
+        <v>98</v>
+      </c>
+      <c r="D17">
+        <v>35.18</v>
+      </c>
+      <c r="E17">
+        <v>1.83</v>
+      </c>
+      <c r="F17">
+        <v>0.1300808479937752</v>
+      </c>
+      <c r="G17">
+        <v>3.15</v>
+      </c>
+      <c r="H17">
+        <v>1.193284017515133</v>
+      </c>
+      <c r="I17">
+        <v>35.59399948120117</v>
+      </c>
+      <c r="J17">
+        <v>33.1295000076294</v>
+      </c>
+      <c r="K17">
+        <v>32.12040004730225</v>
+      </c>
+      <c r="L17">
+        <v>23.47839995384216</v>
+      </c>
+      <c r="M17">
+        <v>1.07</v>
+      </c>
+      <c r="N17">
+        <v>1.11</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17" t="b">
+        <v>0</v>
+      </c>
+      <c r="V17" t="b">
+        <v>1</v>
+      </c>
+      <c r="W17" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>9.57</v>
+      </c>
+      <c r="Y17">
+        <v>36.79</v>
+      </c>
+      <c r="Z17">
+        <v>8.77</v>
+      </c>
+      <c r="AA17">
+        <v>2.84</v>
+      </c>
+      <c r="AB17">
+        <v>153.01</v>
+      </c>
+      <c r="AC17">
+        <v>505.56</v>
+      </c>
+      <c r="AD17">
+        <v>8.49</v>
+      </c>
+      <c r="AE17">
+        <v>11050</v>
+      </c>
+      <c r="AF17">
+        <v>-115.38</v>
+      </c>
+      <c r="AG17">
+        <v>124.07</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>67</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>88</v>
+      </c>
+      <c r="AK17">
+        <v>62.68014552948345</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37">
+      <c r="A18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18">
+        <v>92.32323232323232</v>
+      </c>
+      <c r="C18">
+        <v>306</v>
+      </c>
+      <c r="D18">
+        <v>56.37</v>
+      </c>
+      <c r="E18">
+        <v>1.8</v>
+      </c>
+      <c r="F18">
+        <v>0.07028561948050756</v>
+      </c>
+      <c r="G18">
+        <v>2.12</v>
+      </c>
+      <c r="H18">
+        <v>-0.2894187267877971</v>
+      </c>
+      <c r="I18">
+        <v>57.49300003051758</v>
+      </c>
+      <c r="J18">
+        <v>56.56666660308838</v>
+      </c>
+      <c r="K18">
+        <v>55.28553321838379</v>
+      </c>
+      <c r="L18">
+        <v>45.84321660995484</v>
+      </c>
+      <c r="M18">
+        <v>1.02</v>
+      </c>
+      <c r="N18">
+        <v>1.04</v>
+      </c>
+      <c r="P18">
+        <v>2</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="U18" t="b">
+        <v>0</v>
+      </c>
+      <c r="V18" t="b">
+        <v>0</v>
+      </c>
+      <c r="W18" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>21.49</v>
+      </c>
+      <c r="Y18">
+        <v>58.95</v>
+      </c>
+      <c r="Z18">
+        <v>8.15</v>
+      </c>
+      <c r="AA18">
+        <v>106.56</v>
+      </c>
+      <c r="AB18">
+        <v>23.7</v>
+      </c>
+      <c r="AC18">
+        <v>1875.23</v>
+      </c>
+      <c r="AD18">
+        <v>16.81</v>
+      </c>
+      <c r="AE18">
+        <v>151.12</v>
+      </c>
+      <c r="AF18">
+        <v>1391.86</v>
+      </c>
+      <c r="AG18">
+        <v>-160.89</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>65</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>89</v>
+      </c>
+      <c r="AK18">
+        <v>55.43182443823923</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19">
+        <v>96.56565656565657</v>
+      </c>
+      <c r="C19">
+        <v>287</v>
+      </c>
+      <c r="D19">
+        <v>48.67</v>
+      </c>
+      <c r="E19">
+        <v>1.93</v>
+      </c>
+      <c r="F19">
+        <v>0.3293982763713335</v>
+      </c>
+      <c r="G19">
+        <v>2.6</v>
+      </c>
+      <c r="H19">
+        <v>0.4015495424019181</v>
+      </c>
+      <c r="I19">
+        <v>49.44999923706055</v>
+      </c>
+      <c r="J19">
+        <v>48.58749961853027</v>
+      </c>
+      <c r="K19">
+        <v>46.12439979553223</v>
+      </c>
+      <c r="L19">
+        <v>37.08979983329773</v>
+      </c>
+      <c r="M19">
+        <v>1.02</v>
+      </c>
+      <c r="N19">
+        <v>1.07</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19" t="b">
+        <v>1</v>
+      </c>
+      <c r="V19" t="b">
+        <v>0</v>
+      </c>
+      <c r="W19" t="b">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>14.29</v>
+      </c>
+      <c r="Y19">
+        <v>50.83</v>
+      </c>
+      <c r="Z19">
+        <v>4.81</v>
+      </c>
+      <c r="AA19">
+        <v>-392.99</v>
+      </c>
+      <c r="AB19">
+        <v>34.5</v>
+      </c>
+      <c r="AC19">
+        <v>1387.5</v>
+      </c>
+      <c r="AD19">
+        <v>12.14</v>
+      </c>
+      <c r="AE19">
+        <v>60.81</v>
+      </c>
+      <c r="AF19">
+        <v>8.82</v>
+      </c>
+      <c r="AG19">
+        <v>750</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK19">
+        <v>55.13619354050402</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37">
+      <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20">
+        <v>97.37373737373738</v>
+      </c>
+      <c r="C20">
+        <v>253</v>
+      </c>
+      <c r="D20">
+        <v>34.69</v>
+      </c>
+      <c r="E20">
+        <v>1.89</v>
+      </c>
+      <c r="F20">
+        <v>0.24967130502031</v>
+      </c>
+      <c r="G20">
+        <v>2.18</v>
+      </c>
+      <c r="H20">
+        <v>-0.2030476931390826</v>
+      </c>
+      <c r="I20">
+        <v>34.4239990234375</v>
+      </c>
+      <c r="J20">
+        <v>32.82199983596801</v>
+      </c>
+      <c r="K20">
+        <v>32.59799980163574</v>
+      </c>
+      <c r="L20">
+        <v>24.37379992485046</v>
+      </c>
+      <c r="M20">
+        <v>1.05</v>
+      </c>
+      <c r="N20">
+        <v>1.06</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20" t="b">
+        <v>0</v>
+      </c>
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="W20" t="b">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>11.01</v>
+      </c>
+      <c r="Y20">
+        <v>35.27</v>
+      </c>
+      <c r="Z20">
+        <v>6.13</v>
+      </c>
+      <c r="AA20">
+        <v>-136.86</v>
+      </c>
+      <c r="AB20">
         <v>19.69</v>
       </c>
-      <c r="Z10">
-        <v>3.48</v>
-      </c>
-      <c r="AA10">
-        <v>-211.11</v>
-      </c>
-      <c r="AB10">
-        <v>30.15</v>
-      </c>
-      <c r="AC10">
-        <v>135.38</v>
-      </c>
-      <c r="AD10">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AE10">
-        <v>109.79</v>
-      </c>
-      <c r="AF10">
-        <v>-128.16</v>
-      </c>
-      <c r="AG10">
-        <v>-58.46</v>
-      </c>
-      <c r="AH10" t="s">
-        <v>53</v>
-      </c>
-      <c r="AI10" t="s">
-        <v>59</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>68</v>
-      </c>
-      <c r="AK10">
-        <v>40.57786797226371</v>
+      <c r="AC20">
+        <v>99.61</v>
+      </c>
+      <c r="AD20">
+        <v>2.47</v>
+      </c>
+      <c r="AE20">
+        <v>-118.75</v>
+      </c>
+      <c r="AF20">
+        <v>-23.81</v>
+      </c>
+      <c r="AG20">
+        <v>102.76</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>90</v>
+      </c>
+      <c r="AK20">
+        <v>23.81268089398554</v>
       </c>
     </row>
   </sheetData>
